--- a/data/trans_orig/IP07A14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A14-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24865</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35893</t>
+          <t>35914</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>31704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48710</t>
+          <t>48135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63862</t>
+          <t>63896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23634</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>24654</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30459</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110391</t>
+          <t>109915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133744</t>
+          <t>132307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141041</t>
+          <t>141442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165501</t>
+          <t>164573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259137</t>
+          <t>259720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291686</t>
+          <t>290463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60822</t>
+          <t>60671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83573</t>
+          <t>83255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65650</t>
+          <t>66003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88042</t>
+          <t>88868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134507</t>
+          <t>134225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165672</t>
+          <t>164061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>29475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42524</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>28866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41362</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61268</t>
+          <t>60909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79543</t>
+          <t>79039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28645</t>
+          <t>29515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42698</t>
+          <t>43571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60949</t>
+          <t>60486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173881</t>
+          <t>174321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202363</t>
+          <t>202776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>200880</t>
+          <t>200621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>229271</t>
+          <t>229733</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>382105</t>
+          <t>383336</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>422273</t>
+          <t>424445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>104517</t>
+          <t>105433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133432</t>
+          <t>133922</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104025</t>
+          <t>103871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>131365</t>
+          <t>132051</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217383</t>
+          <t>216791</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>257534</t>
+          <t>258134</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>32646</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32369</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69777</t>
+          <t>69746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21528</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24311</t>
+          <t>24275</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27831</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44119</t>
+          <t>42989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108359</t>
+          <t>110863</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131605</t>
+          <t>132983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138087</t>
+          <t>137971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162066</t>
+          <t>161512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254193</t>
+          <t>254547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287749</t>
+          <t>287248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67503</t>
+          <t>67172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90410</t>
+          <t>88725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54969</t>
+          <t>54914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76624</t>
+          <t>78137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127039</t>
+          <t>128020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159647</t>
+          <t>160192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24153</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>32766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>46225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34929</t>
+          <t>33587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46095</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71324</t>
+          <t>70320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88687</t>
+          <t>88249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29716</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21083</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>30285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46955</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182340</t>
+          <t>180646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210974</t>
+          <t>210346</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204120</t>
+          <t>203541</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231921</t>
+          <t>229957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>392738</t>
+          <t>394004</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>432944</t>
+          <t>434928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102400</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130750</t>
+          <t>131685</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>85080</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112838</t>
+          <t>113729</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>195150</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>237598</t>
+          <t>236079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>15176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35212</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48759</t>
+          <t>48209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29686</t>
+          <t>29804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145175</t>
+          <t>143462</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170831</t>
+          <t>169038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152323</t>
+          <t>152740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176823</t>
+          <t>177676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303183</t>
+          <t>305197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340874</t>
+          <t>340934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,77%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69903</t>
+          <t>70013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94267</t>
+          <t>95660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60122</t>
+          <t>59529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>82878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136164</t>
+          <t>136500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>171312</t>
+          <t>170034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41340</t>
+          <t>41491</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54836</t>
+          <t>55109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48224</t>
+          <t>47298</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61414</t>
+          <t>61048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93974</t>
+          <t>93065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112302</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,87%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36847</t>
+          <t>37223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55046</t>
+          <t>56565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -8240,82 +8240,82 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6156</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>640</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6543</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>212762</t>
+          <t>212785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>242260</t>
+          <t>241958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>225622</t>
+          <t>226462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>253489</t>
+          <t>254945</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>445240</t>
+          <t>443888</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>488932</t>
+          <t>485465</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101117</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130493</t>
+          <t>128408</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95367</t>
+          <t>94434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>122534</t>
+          <t>121460</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>201472</t>
+          <t>204383</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>242365</t>
+          <t>243942</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,82 +8937,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>10760</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>6362</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>16910</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>25157</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>17768</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>34209</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>10760</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>16957</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>25157</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>18560</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>35355</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A14-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A14-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26391</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21050</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31627</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>30289</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24888</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35914</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24408</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35820</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>59,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26391</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20900</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31704</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,88%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>48622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63896</t>
+          <t>64867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>66,26%</t>
         </is>
       </c>
     </row>
@@ -840,67 +840,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>18883</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13800</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24327</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>18386</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13125</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23743</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12958</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24161</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18883</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14007</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24654</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29640</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>44728</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -953,67 +953,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5320</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>630</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5961</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,94%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5203</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50674</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>153604</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>140786</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>164596</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>64,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>59,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>121856</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>109915</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>132307</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>108529</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>132289</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>60,13%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>153604</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>141442</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>164573</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259720</t>
+          <t>259762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290463</t>
+          <t>291599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76585</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65858</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88028</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72106</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60671</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83255</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62340</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>86202</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,58%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76585</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66003</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>88868</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134225</t>
+          <t>133315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164061</t>
+          <t>162992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7773</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7350</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4062</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12873</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3983</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12361</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7773</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13581</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3899</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1856,74 +1856,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237963</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202670</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35318</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28652</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40876</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,44%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35925</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29475</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42174</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28884</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42204</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,74%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>35318</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28866</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>41283</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>58,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60909</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79039</t>
+          <t>79886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16497</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28378</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28869</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22780</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>36003</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22676</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35532</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,18%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22251</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16511</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>29515</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43571</t>
+          <t>42637</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60486</t>
+          <t>59639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,87%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6835</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2060</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6335</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7708</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60394</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>66854</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>215313</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>200700</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>228387</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>62,3%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58,08%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>66,09%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>188071</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>174321</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>202776</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>173879</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>203056</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>58,74%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>54,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>63,33%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>215313</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>200621</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>229733</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>383336</t>
+          <t>382305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>424445</t>
+          <t>423354</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>117720</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>104437</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>131303</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>119361</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>105433</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>133922</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>105201</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>132781</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>37,28%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>41,82%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>117720</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>103871</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>132051</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>34,06%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>216791</t>
+          <t>216659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258134</t>
+          <t>256071</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12554</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8028</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>19918</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>11409</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6780</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>18268</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>6923</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>17763</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>3,56%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>12554</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>8009</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>19234</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>33777</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3107,107 +3107,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4154</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3970</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -3220,107 +3220,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3305</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3317</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>320198</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>320198</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>320198</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26966</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21299</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32471</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35245</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29193</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40699</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29410</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40818</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>66,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26966</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21578</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32205</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>58,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>53660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69746</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18887</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13382</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24554</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>53,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16102</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11023</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21926</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10932</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22016</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>30,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18887</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13648</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24275</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>41,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27808</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>43080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -3907,107 +3907,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1736</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5050</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1736</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5542</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1736</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>6071</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>150319</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>138267</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>161721</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>120900</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>110863</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>132983</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>110029</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>132452</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>59,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>150319</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>137971</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>161512</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254547</t>
+          <t>254440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287248</t>
+          <t>287155</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65043</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>55100</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78395</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>78228</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67172</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>88725</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66879</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>88809</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,33%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65043</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54914</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78137</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128020</t>
+          <t>126969</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>159732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10644</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6414</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16556</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>5628</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2684</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10534</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10998</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2,75%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10644</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5956</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16147</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -4702,107 +4702,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1271</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4644</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4484</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3924</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227278</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227278</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227278</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204757</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204757</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204757</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227278</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227278</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>40096</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33895</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>45469</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>69,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>40438</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>32766</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>46225</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34200</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>63,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>72,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40096</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>33587</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>45169</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>69,21%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70320</t>
+          <t>71812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>89521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15539</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10387</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21278</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>22305</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16611</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29945</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15722</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>28233</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>15539</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>10786</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>22097</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,82%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47945</t>
+          <t>46788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -5271,84 +5271,84 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>2297</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5823</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2297</t>
-        </is>
-      </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
           <t>634</t>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5497,107 +5497,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3475</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3821</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3880</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3350</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>217381</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>203373</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>230489</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>65,66%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>61,43%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>69,62%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>196583</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>180646</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>210346</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>182568</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>210898</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>61,19%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>217381</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>203541</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>229957</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>65,66%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394004</t>
+          <t>393286</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434928</t>
+          <t>433692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>99470</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>87098</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>113992</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>26,31%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>34,43%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>116635</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>102923</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>131685</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>102445</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>131166</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>36,31%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,04%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>99470</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>88574</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>113729</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195150</t>
+          <t>196485</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>236079</t>
+          <t>237100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12942</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8292</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>19300</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>7365</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3709</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>12874</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12614</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>12942</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>19324</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29077</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6066,107 +6066,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>1271</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4572</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4396</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1271</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4169</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4398</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>331064</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>331064</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>331064</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321258</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321258</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321258</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>331064</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>331064</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>331064</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20113</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13956</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24855</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21640</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16535</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25724</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16603</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25552</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>68,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20113</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15176</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>25908</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>54,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34736</t>
+          <t>35276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48209</t>
+          <t>48990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14170</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19814</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8780</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5286</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13845</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13387</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14170</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9182</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19740</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1394</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4829</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4183</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6386</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>165334</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>152920</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>177531</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>62,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>157129</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>143462</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>169038</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>144106</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>169465</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>165334</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>152740</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>177676</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>67,43%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305197</t>
+          <t>304800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340934</t>
+          <t>339096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71451</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59981</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>83559</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>82061</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70013</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>95660</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69628</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>93684</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>32,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71451</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>59529</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82878</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>29,14%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136500</t>
+          <t>137210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170034</t>
+          <t>170839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4346</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13851</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10377</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6165</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16427</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>16590</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8405</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4790</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14602</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>26383</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -7774,107 +7774,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4999</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5227</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4698</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5355</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>245190</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>245190</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>245190</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>360</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>250559</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>245190</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>245190</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>245190</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54986</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47782</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>61221</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>71,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>48534</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>41491</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55109</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41439</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>54797</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,24%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>55,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54986</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>47298</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>61048</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>71,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93065</t>
+          <t>93522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112099</t>
+          <t>112761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22357</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16122</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29561</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23238</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16911</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29944</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17247</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22357</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30045</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37223</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56565</t>
+          <t>56229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6224</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>77343</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>77343</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>77343</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>77343</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>77343</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>77343</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>240433</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>226207</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>255986</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66,94%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>62,98%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>71,27%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>327</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>227303</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>212785</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>241958</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>213326</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>242897</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>63,71%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>59,64%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,82%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>240433</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>226462</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>254945</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>66,94%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>443888</t>
+          <t>444948</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>485465</t>
+          <t>489104</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>107979</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>92389</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>121937</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>30,06%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>25,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>33,95%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>114080</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>99988</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>128408</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>98940</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>128045</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>31,98%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>28,03%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>107979</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>94434</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>121460</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>30,06%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>204383</t>
+          <t>202200</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243942</t>
+          <t>244798</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10760</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>17013</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>14397</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>9293</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>21931</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>9271</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>21747</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,04%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>10760</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>6362</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>16910</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>33602</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -9138,107 +9138,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4972</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4959</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4617</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>359172</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>359172</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>359172</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>356772</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>359172</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>359172</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>359172</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
